--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,530 +784,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135121278</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>442483</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7047683</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121278</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135121292</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7047784</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121292</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121293</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>442387</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7047735</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121293</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121294</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>442493</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7047717</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121294</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,530 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135121278</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442483</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047683</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121278</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135121292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121292</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>442387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121293</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442493</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047717</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121294</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135121278</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135121292</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135121293</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>135121294</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,530 +784,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135121278</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>442483</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7047683</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121278</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135121292</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7047784</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121292</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121293</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>442387</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7047735</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121293</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121294</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>442493</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7047717</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121294</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,530 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135121278</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442483</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047683</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121278</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135121292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121292</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>442387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121293</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442493</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047717</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121294</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135121278</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135121292</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135121293</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>135121294</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135121278</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135121292</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135121293</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>135121294</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135121278</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135121292</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135121293</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>135121294</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135121278</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135121292</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135121293</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>135121294</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,530 +784,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135121278</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>442483</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7047683</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121278</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135121292</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7047784</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121292</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121293</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>442387</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7047735</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121293</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121294</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Koltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>442493</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7047717</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121294</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,530 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135121278</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442483</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047683</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121278</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135121292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121292</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>442387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121293</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442493</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047717</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121294</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
